--- a/data/trans_camb/P1401-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1401-Habitat-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,74</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,8</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,82</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,85</t>
+          <t>-1,09; 1,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 1,82</t>
+          <t>-0,3; 2,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 2,43</t>
+          <t>-0,66; 2,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,91</t>
+          <t>-0,59; 1,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,27</t>
+          <t>-0,61; 1,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 1,52</t>
+          <t>-0,07; 1,64</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>60,99%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-78,56; 197,59</t>
+          <t>-76,05; 236,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-32,2; 342,05</t>
+          <t>-26,23; 370,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-36,11; 241,33</t>
+          <t>-34,65; 253,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-29,37; 212,52</t>
+          <t>-27,06; 211,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,02; 143,82</t>
+          <t>-35,8; 138,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 185,68</t>
+          <t>-4,83; 174,66</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,26</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>0,79</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,73</t>
+          <t>-0,87; 0,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,95</t>
+          <t>0,25; 2,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,69</t>
+          <t>-1,51; 0,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,55</t>
+          <t>-0,87; 1,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,51</t>
+          <t>-0,93; 0,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 1,47</t>
+          <t>-0,0; 1,53</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>125,38%</t>
+          <t>167,41%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>59,44%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-73,65; 202,62</t>
+          <t>-71,08; 322,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-34,84; 499,04</t>
+          <t>-0,46; 805,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-64,03; 55,74</t>
+          <t>-60,76; 60,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-28,1; 118,13</t>
+          <t>-34,29; 113,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,68; 53,5</t>
+          <t>-57,42; 53,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 151,07</t>
+          <t>-0,42; 164,55</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,1</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,55</t>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,39</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,48</t>
+          <t>-1,23; 0,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 2,4</t>
+          <t>-0,06; 2,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,86</t>
+          <t>-1,74; 0,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,57</t>
+          <t>-1,64; 0,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,41</t>
+          <t>-1,27; 0,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 1,1</t>
+          <t>-0,52; 1,22</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>120,99%</t>
+          <t>112,68%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-32,0%</t>
+          <t>-13,97%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>29,25%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-84,15; 135,64</t>
+          <t>-85,3; 157,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,56; 518,67</t>
+          <t>-13,43; 495,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-68,3; 94,07</t>
+          <t>-70,68; 104,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-76,35; 62,1</t>
+          <t>-59,98; 102,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-66,75; 54,5</t>
+          <t>-65,35; 53,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,39; 116,57</t>
+          <t>-28,35; 151,42</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,45</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 0,42</t>
+          <t>-1,8; 0,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,07</t>
+          <t>-0,58; 1,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 1,71</t>
+          <t>-1,43; 1,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 1,27</t>
+          <t>-1,19; 1,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,74</t>
+          <t>-1,14; 0,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,21</t>
+          <t>-0,56; 1,3</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-72,5; 39,46</t>
+          <t>-71,29; 38,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-28,12; 167,9</t>
+          <t>-25,72; 178,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,65; 90,46</t>
+          <t>-40,24; 94,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-41,82; 73,99</t>
+          <t>-33,55; 81,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-42,25; 42,12</t>
+          <t>-42,91; 45,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-24,6; 70,55</t>
+          <t>-20,46; 75,37</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,61</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,24</t>
+          <t>-0,74; 0,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,49</t>
+          <t>0,36; 1,54</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,69</t>
+          <t>-0,76; 0,74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,74</t>
+          <t>-0,38; 0,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,3</t>
+          <t>-0,57; 0,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,01; 0,92</t>
+          <t>0,22; 1,07</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>38,42%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-52,97; 30,24</t>
+          <t>-51,9; 28,49</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>20,82; 175,9</t>
+          <t>24,85; 175,55</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-29,1; 41,74</t>
+          <t>-32,14; 45,22</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-25,1; 43,4</t>
+          <t>-16,43; 50,95</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-32,4; 22,78</t>
+          <t>-31,67; 21,13</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,41; 65,89</t>
+          <t>11,23; 79,32</t>
         </is>
       </c>
     </row>
